--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.60374411723033</v>
+        <v>5.948108419049928</v>
       </c>
       <c r="D2" t="n">
-        <v>36.11662123172133</v>
+        <v>5.868950950154716</v>
       </c>
       <c r="E2" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F2" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.43774470738777</v>
+        <v>4.946133514950513</v>
       </c>
       <c r="D3" t="n">
-        <v>30.22293403108312</v>
+        <v>4.911226780051008</v>
       </c>
       <c r="E3" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F3" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.39876860099125</v>
+        <v>5.427299897661078</v>
       </c>
       <c r="D4" t="n">
-        <v>33.48253830776724</v>
+        <v>5.440912475012177</v>
       </c>
       <c r="E4" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F4" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.32193815089139</v>
+        <v>3.464814949519851</v>
       </c>
       <c r="D5" t="n">
-        <v>21.37057469965916</v>
+        <v>3.472718388694613</v>
       </c>
       <c r="E5" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F5" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.87106579317751</v>
+        <v>5.829048191391345</v>
       </c>
       <c r="D6" t="n">
-        <v>35.37811364885965</v>
+        <v>5.748943467939694</v>
       </c>
       <c r="E6" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F6" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.478289230104358</v>
+        <v>1.215221999891958</v>
       </c>
       <c r="D7" t="n">
-        <v>7.019366216013463</v>
+        <v>1.140647010102188</v>
       </c>
       <c r="E7" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F7" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.461033280002107</v>
+        <v>0.3999179080003424</v>
       </c>
       <c r="D8" t="n">
-        <v>31.789978394424</v>
+        <v>5.1658714890939</v>
       </c>
       <c r="E8" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F8" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.90279626795364</v>
+        <v>4.209204393542468</v>
       </c>
       <c r="D9" t="n">
-        <v>23.42510391585398</v>
+        <v>3.806579386326272</v>
       </c>
       <c r="E9" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F9" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.55983424175242</v>
+        <v>5.290973064284769</v>
       </c>
       <c r="D10" t="n">
-        <v>33.01203108298549</v>
+        <v>5.364455050985143</v>
       </c>
       <c r="E10" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F10" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.91989391612623</v>
+        <v>3.886982761370512</v>
       </c>
       <c r="D11" t="n">
-        <v>23.56559528148423</v>
+        <v>3.829409233241187</v>
       </c>
       <c r="E11" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F11" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.26505338240841</v>
+        <v>5.568071174641367</v>
       </c>
       <c r="D12" t="n">
-        <v>4.111592313398951</v>
+        <v>0.6681337509273296</v>
       </c>
       <c r="E12" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F12" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.29113390742297</v>
+        <v>2.159809259956233</v>
       </c>
       <c r="D13" t="n">
-        <v>15.45512805741964</v>
+        <v>2.511458309330691</v>
       </c>
       <c r="E13" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F13" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.7614305035725</v>
+        <v>4.511232456830531</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4955791116008284</v>
+        <v>0.08053160563513462</v>
       </c>
       <c r="E14" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F14" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.88798005083631</v>
+        <v>5.019296758260901</v>
       </c>
       <c r="D15" t="n">
-        <v>43.63475797414108</v>
+        <v>7.090648170797926</v>
       </c>
       <c r="E15" t="n">
-        <v>10.36178813869018</v>
+        <v>1.683790572537154</v>
       </c>
       <c r="F15" t="n">
-        <v>12.67297591404084</v>
+        <v>2.059358586031636</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
